--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suzuk\OneDrive\デスクトップ\progtest\factrysim_mini\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473D8E9D-848E-46BF-A8F0-6F8C73526BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C6297F-3927-4312-B17E-1D4FCA1F65BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="120">
   <si>
     <t>説明</t>
   </si>
@@ -231,35 +231,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>後工程(workOut)へ搬送開始
- → 後工程(agvOut)待ちに到達</t>
-    <rPh sb="0" eb="1">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ハンソウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>トウタツ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>後工程(agvOut)への搬送開始
  → 前工程(agvIn)待ちに到達</t>
     <phoneticPr fontId="18"/>
@@ -648,91 +619,6 @@
   </si>
   <si>
     <t>agv_process</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がagvOut_wait状態である
-自工程がagvを後工程(agvOut)へ出力</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait_1状態である
-自工程がworkを後工程(workOut)へ出力
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="24" eb="27">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>アトコウテイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait_2状態である
-自工程がworkを後工程(workOut)へ出力
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait_3状態である
-自工程がworkを後工程(workOut)へ出力
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait_n状態である
-自工程がworkを後工程(workOut)へ出力
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait状態である
-自工程がworkを後工程(workOut)へ出力
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がwait状態である
-自工程がworkを後工程(workOut)へ出力</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -741,6 +627,225 @@
     <rPh sb="8" eb="10">
       <t>ジョウタイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait状態である
+workOutポートに接続あり</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(workOut)へworkを搬送開始
+ → 後工程(agvOut)待ちに到達</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハンソウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がwait状態である</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がagvOut_wait状態である</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(workOut)へwork1を搬送開始
+ → 後工程(agvOut)待ちに到達</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンソウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(workOut)へwork2を搬送開始
+ → 後工程(agvOut)待ちに到達</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンソウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(workOut)へwork nを搬送開始
+ → 後工程(agvOut)待ちに到達</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンソウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(workOut)へwork3を搬送開始
+ → 後工程(agvOut)待ちに到達</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンソウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait_n状態である
+workOutポートに接続あり</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait_3状態である
+workOutポートに接続あり</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait_2状態である
+workOutポートに接続あり</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait_1状態である
+workOutポートに接続あり</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>後工程(agvOut)へのAGV搬送開始
+ → 前工程(agvIn)待ちに到達</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1797,12 +1902,12 @@
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
@@ -1822,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
@@ -1836,19 +1941,19 @@
         <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
@@ -1859,19 +1964,19 @@
         <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
@@ -1882,19 +1987,19 @@
         <v>22</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
@@ -1905,24 +2010,24 @@
         <v>15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
@@ -1942,7 +2047,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>18</v>
@@ -1956,42 +2061,42 @@
         <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B15" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
@@ -2002,19 +2107,19 @@
         <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.4">
@@ -2022,22 +2127,22 @@
         <v>6</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
@@ -2048,47 +2153,47 @@
         <v>25</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.4">
@@ -2108,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>18</v>
@@ -2122,42 +2227,42 @@
         <v>26</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
@@ -2168,139 +2273,139 @@
         <v>27</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B29" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B31" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B32" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.4">
@@ -2320,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>18</v>
@@ -2328,168 +2433,168 @@
     </row>
     <row r="36" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B37" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B41" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="1"/>
@@ -2500,191 +2605,191 @@
     </row>
     <row r="44" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B44" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B47" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B47" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="C47" s="7" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B49" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B49" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="C49" s="7" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B51" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B51" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="C51" s="7" t="s">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="1"/>
@@ -2695,117 +2800,117 @@
     </row>
     <row r="53" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B53" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B54" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="C54" s="7" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B55" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B56" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B57" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C6297F-3927-4312-B17E-1D4FCA1F65BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C51F94E-1DCF-48D5-8DDB-38DA733B5B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C51F94E-1DCF-48D5-8DDB-38DA733B5B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A708F495-8E04-4C26-A58D-4FBCA7C332B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,14 +622,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がwait状態である
-自工程がworkを後工程(workOut)へ出力</t>
-    <rPh sb="8" eb="10">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>自工程がworkOut_wait状態である
 workOutポートに接続あり</t>
     <rPh sb="0" eb="3">
@@ -846,6 +838,13 @@
   <si>
     <t>後工程(agvOut)へのAGV搬送開始
  → 前工程(agvIn)待ちに到達</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がwait状態である</t>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1990,7 +1989,7 @@
         <v>36</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>70</v>
@@ -2156,7 +2155,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>68</v>
@@ -2316,13 +2315,13 @@
         <v>46</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>68</v>
@@ -2368,7 +2367,7 @@
         <v>36</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>69</v>
@@ -2677,13 +2676,13 @@
         <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>68</v>
@@ -2723,13 +2722,13 @@
         <v>90</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>68</v>
@@ -2769,13 +2768,13 @@
         <v>92</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>68</v>
@@ -2826,13 +2825,13 @@
         <v>94</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>68</v>
@@ -2872,13 +2871,13 @@
         <v>47</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>69</v>

--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A708F495-8E04-4C26-A58D-4FBCA7C332B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01EBE56-AA47-48D7-B691-62443E8FCB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="work_node_memo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="120">
   <si>
     <t>説明</t>
   </si>
@@ -277,21 +290,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>workInポートに接続ない場合はスキップ</t>
-    <rPh sb="14" eb="16">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>workInポートに接続ない場合はスキップ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>workOutポートに接続ない場合はスキップ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>workIn_idle</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -316,32 +314,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がagv_process完了かつ
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_process完了かつ
-workOutポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn1_idle状態である</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>自工程がprocess1完了</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn2_idle状態である</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がidle状態である</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイジョウタイ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -404,18 +377,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がagvIn_idle状態である</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_idle状態である
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>前工程(workIn2)がworkを出力</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -506,27 +467,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkIn_idle_1状態である
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_idle_2状態である
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_idle_3状態である
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>workIn_process_n</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_idle_n状態である
-workInポートに接続あり</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -572,41 +513,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkIn_process_n完了かつ
-workOutポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_process_1完了かつ
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_process_2完了かつ
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn_process_n-1完了かつ
-workInポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_down_1完了かつ
-workOutポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_down_2完了かつ
-workOutポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_down_n-1完了かつ
-workOutポートに接続あり</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>workOut_down_n完了</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -619,17 +525,6 @@
   </si>
   <si>
     <t>agv_process</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkOut_wait状態である
-workOutポートに接続あり</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジョウタイ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -662,20 +557,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がwait状態である</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がagvOut_wait状態である</t>
-    <rPh sb="0" eb="3">
-      <t>ジコウテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>後工程(workOut)へwork1を搬送開始
  → 後工程(agvOut)待ちに到達</t>
     <rPh sb="0" eb="1">
@@ -792,19 +673,112 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkOut_wait_n状態である
-workOutポートに接続あり</t>
+    <t>後工程(agvOut)へのAGV搬送開始
+ → 前工程(agvIn)待ちに到達</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がagvOut_wait状態である
+agvOutポートに接続あり（ない場合はwaitのまま）</t>
     <rPh sb="0" eb="3">
       <t>ジコウテイ</t>
     </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がagvIn_idle状態である
+workInポートに接続あり（ない場合はidleのまま）</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がidle状態である
+workInポートに接続あり（ない場合はidleのまま）</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn1_idle状態である
+workInポートに接続あり（ない場合はidleのまま）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn2_idle状態である
+workInポートに接続あり（ない場合はidleのまま）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がwait状態である
+workOutポートに接続あり（ない場合はwaitのまま）</t>
+    <rPh sb="8" eb="10">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がwait状態である
+workOutポートに接続あり（ない場合はwaitのまま）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>次の状態</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>workIn_idle_4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>workOut_wait_4</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_idle_1状態である
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_idle_2状態である
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_idle_3状態である
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_idle_n状態である
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait_1状態である
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
     <rPh sb="18" eb="20">
       <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkOut_wait_3状態である
-workOutポートに接続あり</t>
+    <t>自工程がworkOut_wait_2状態である
+workOutポートに接続あり（ない場合はスキップ）</t>
     <rPh sb="0" eb="3">
       <t>ジコウテイ</t>
     </rPh>
@@ -814,8 +788,8 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkOut_wait_2状態である
-workOutポートに接続あり</t>
+    <t>自工程がworkOut_wait_3状態である
+workOutポートに接続あり（ない場合はスキップ）</t>
     <rPh sb="0" eb="3">
       <t>ジコウテイ</t>
     </rPh>
@@ -825,8 +799,8 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkOut_wait_1状態である
-workOutポートに接続あり</t>
+    <t>自工程がworkOut_wait_n状態である
+workOutポートに接続あり（ない場合はスキップ）</t>
     <rPh sb="0" eb="3">
       <t>ジコウテイ</t>
     </rPh>
@@ -836,14 +810,66 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>後工程(agvOut)へのAGV搬送開始
- → 前工程(agvIn)待ちに到達</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がwait状態である</t>
-    <rPh sb="8" eb="10">
+    <t>自工程がagv_process完了かつ
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_process_1完了かつ
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_process_2完了かつ
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_idle状態である
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_process_n完了かつ
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_down_1完了かつ
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_down_2完了かつ
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_down_n-1完了かつ
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_process_n-1完了かつ
+workInポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn_process完了
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkOut_wait状態である
+workOutポートに接続あり（ない場合はスキップ）</t>
+    <rPh sb="0" eb="3">
+      <t>ジコウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
       <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -1569,6 +1595,1443 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>278059</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>147312</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38454</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F419190D-F697-0FD2-F5C7-AC2A175777AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19709059" y="646043"/>
+          <a:ext cx="8524579" cy="9961020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Equipment</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>equipment_node</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>自己遷移の明示</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>process</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>：処理時間未満は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>process</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>継続</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>wait</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>：後工程が受入不可なら </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>wait</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>継続</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>down</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>：ダウン時間未満は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>down</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>継続</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>idle</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>workIn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続／入力なしなら </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>idle</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>継続</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>workIn</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続時の振る舞い</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>表では省略されているので「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>idle</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>継続」を補足すると明確。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Merge2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>merge2_node</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>ミスマッチ時の遷移</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>仕様上は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ERROR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>（あるいは </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>reset</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>）に落ちる扱いですが表に無い。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>入力</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>待ちのときの受け入れ制御</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>workIn2_idle</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>のときは </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>input1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>を受け入れない</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>これを表の条件に明記するとミスマッチ対策が明確。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>自己遷移の明示</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>process1/2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>は時間経過まで同状態維持</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>wait</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>downstream </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>が受入不可なら維持</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>down</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>は時間経過まで維持</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>AGV Route</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>max_load=1 / n</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>agvOut</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続時の処理</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>実装は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>agvOut_wait</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>に入る前に </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>即 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>idle </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>へ戻る</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>_resetToIdle</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>表に「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>agvOut</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続時は </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>skip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>」等の明記があると整合が取れる。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>agvOut_down </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>の受入待ち延長</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>downstream </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>が受け入れないと </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>downTime </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>を延長</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>し続ける（自己遷移）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>表では「待ち続ける」旨の記述があると安全。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>workIn/workOut </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続のスキップ</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="1"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>注記で書かれているので</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>OK</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>。ただし</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>workIn_*</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>系が </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>一括スキップ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>され </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>workOut_wait_1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>へ移ること</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="2"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>workOut</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>未接続なら </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>agvOut_wait</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>へ直行</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>を状態遷移表に書くとより明確です。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="ja-JP" altLang="en-US">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>結論</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>「暗黙の自己遷移は省略」という前提なら整合は取れています。</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>ただし、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>ミスマッチ防止や接続未設定時の挙動</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>を明記するなら上記を追記した方が安全です。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>必要なら、あなたの表フォーマットに合わせて「追加行案」を作成します。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -1886,30 +3349,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0103435C-BE91-42D6-9B0B-E3F858993823}">
-  <dimension ref="B1:H57"/>
+  <dimension ref="B1:I57"/>
   <sheetFormatPr defaultColWidth="113.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
     <col min="2" max="2" width="18.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.25" customWidth="1"/>
     <col min="6" max="6" width="38.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.75" customWidth="1"/>
+    <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1926,13 +3390,16 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1942,20 +3409,24 @@
       <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>53</v>
+      <c r="E5" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>58</v>
+      <c r="G5" s="2" t="str">
+        <f>B6</f>
+        <v>wait</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1966,19 +3437,23 @@
         <v>36</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>66</v>
+      <c r="G6" s="4" t="str">
+        <f t="shared" ref="G6:G7" si="0">B7</f>
+        <v>down</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -1989,19 +3464,23 @@
         <v>36</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="G7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>idle</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
@@ -2012,24 +3491,28 @@
         <v>36</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>60</v>
+      <c r="G8" s="8" t="str">
+        <f>B5</f>
+        <v>process</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -2046,13 +3529,16 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -2062,22 +3548,26 @@
       <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
+      <c r="E14" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>58</v>
+      <c r="G14" s="2" t="str">
+        <f>B15</f>
+        <v>workIn2_idle</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>13</v>
@@ -2086,19 +3576,23 @@
         <v>36</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>60</v>
+      <c r="G15" s="8" t="str">
+        <f t="shared" ref="G15:G18" si="1">B16</f>
+        <v>process2</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
@@ -2106,22 +3600,24 @@
         <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>58</v>
+      <c r="G16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>wait</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2132,19 +3628,23 @@
         <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>66</v>
+      <c r="G17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>down</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
@@ -2155,21 +3655,25 @@
         <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G18" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>workIn1_idle</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>14</v>
@@ -2178,24 +3682,28 @@
         <v>36</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>60</v>
+      <c r="G19" s="8" t="str">
+        <f>B14</f>
+        <v>process1</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2212,13 +3720,16 @@
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
         <v>1</v>
       </c>
@@ -2228,22 +3739,26 @@
       <c r="D25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>62</v>
+      <c r="E25" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>58</v>
+      <c r="G25" s="2" t="str">
+        <f>B26</f>
+        <v>workIn_idle</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>29</v>
@@ -2252,19 +3767,23 @@
         <v>36</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G26" s="8" t="str">
+        <f t="shared" ref="G26:G31" si="2">B27</f>
+        <v>workIn_process</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B27" s="2" t="s">
         <v>19</v>
       </c>
@@ -2275,19 +3794,23 @@
         <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>58</v>
+      <c r="G27" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>workOut_wait</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
         <v>31</v>
       </c>
@@ -2298,42 +3821,50 @@
         <v>36</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>workOut_down</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B29" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G29" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>agvOut_wait</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B30" s="4" t="s">
         <v>33</v>
       </c>
@@ -2343,22 +3874,26 @@
       <c r="D30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>67</v>
+      <c r="E30" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>66</v>
+      <c r="G30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>agvOut_down</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B31" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>28</v>
@@ -2367,21 +3902,25 @@
         <v>36</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="G31" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>agvIn_idle</v>
+      </c>
       <c r="H31" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B32" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>17</v>
@@ -2390,24 +3929,28 @@
         <v>36</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>60</v>
+      <c r="G32" s="8" t="str">
+        <f>B25</f>
+        <v>agv_process</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
@@ -2424,15 +3967,18 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="H35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>26</v>
@@ -2440,22 +3986,26 @@
       <c r="D36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>62</v>
+      <c r="E36" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>58</v>
+      <c r="G36" s="2" t="str">
+        <f>B37</f>
+        <v>workIn_idle_1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B37" s="8" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>29</v>
@@ -2464,21 +4014,25 @@
         <v>36</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G37" s="8" t="str">
+        <f t="shared" ref="G37:G41" si="3">B38</f>
+        <v>workIn_process_1</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>27</v>
@@ -2487,21 +4041,25 @@
         <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>58</v>
+      <c r="G38" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>workIn_idle_2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>29</v>
@@ -2510,21 +4068,25 @@
         <v>36</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G39" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>workIn_process_2</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>27</v>
@@ -2533,21 +4095,25 @@
         <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>58</v>
+      <c r="G40" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>workIn_idle_3</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B41" s="8" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>29</v>
@@ -2556,21 +4122,25 @@
         <v>36</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G41" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>workIn_process_3</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>27</v>
@@ -2579,21 +4149,24 @@
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="1"/>
@@ -2601,10 +4174,11 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B44" s="8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>29</v>
@@ -2613,21 +4187,25 @@
         <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G44" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G44" s="8" t="str">
+        <f>B45</f>
+        <v>workIn_process_n</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B45" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>27</v>
@@ -2636,21 +4214,25 @@
         <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>58</v>
+      <c r="G45" s="2" t="str">
+        <f t="shared" ref="G45:G50" si="4">B46</f>
+        <v>workOut_wait_1</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B46" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>30</v>
@@ -2659,44 +4241,52 @@
         <v>36</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>workOut_down_1</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G47" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>workOut_wait_2</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>30</v>
@@ -2705,44 +4295,52 @@
         <v>36</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>workOut_down_2</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B49" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G49" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>workOut_wait_3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>30</v>
@@ -2751,44 +4349,51 @@
         <v>36</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>workOut_down_3</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B51" s="6" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B52" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="1"/>
@@ -2796,10 +4401,11 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-    </row>
-    <row r="53" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B53" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>30</v>
@@ -2808,42 +4414,50 @@
         <v>36</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="G53" s="4" t="str">
+        <f>B54</f>
+        <v>workOut_down_n</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B54" s="6" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G54" s="6" t="str">
+        <f t="shared" ref="G54:G56" si="5">B55</f>
+        <v>agvOut_wait</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B55" s="4" t="s">
         <v>33</v>
       </c>
@@ -2853,45 +4467,53 @@
       <c r="D55" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>103</v>
+      <c r="E55" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>66</v>
+      <c r="G55" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>agvOut_down</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B56" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G56" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="G56" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>agvIn_idle</v>
+      </c>
       <c r="H56" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B57" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>17</v>
@@ -2900,15 +4522,19 @@
         <v>36</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G57" s="8" t="s">
-        <v>60</v>
+      <c r="G57" s="8" t="str">
+        <f>B36</f>
+        <v>agv_process</v>
       </c>
       <c r="H57" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I57" s="8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2916,5 +4542,6 @@
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01EBE56-AA47-48D7-B691-62443E8FCB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF73B18F-5663-4FBF-A705-9352786C81E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="120">
   <si>
     <t>説明</t>
   </si>
@@ -705,16 +705,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>自工程がworkIn1_idle状態である
-workInポートに接続あり（ない場合はidleのまま）</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>自工程がworkIn2_idle状態である
-workInポートに接続あり（ない場合はidleのまま）</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>自工程がwait状態である
 workOutポートに接続あり（ない場合はwaitのまま）</t>
     <rPh sb="8" eb="10">
@@ -871,6 +861,26 @@
     <rPh sb="40" eb="42">
       <t>バアイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn2_idle状態である
+workIn2ポートに接続あり（ない場合はidleのまま）
+IDミスマッチ時はError停止（workIn2を受け入れない）</t>
+    <rPh sb="66" eb="68">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自工程がworkIn1_idle状態である
+workIn1ポートに接続あり（ない場合はidleのまま）</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -3390,7 +3400,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>53</v>
@@ -3464,7 +3474,7 @@
         <v>36</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>60</v>
@@ -3529,7 +3539,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>53</v>
@@ -3549,7 +3559,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>34</v>
@@ -3592,7 +3602,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
@@ -3603,7 +3613,7 @@
         <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>34</v>
@@ -3615,7 +3625,9 @@
       <c r="H16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="4" t="s">
@@ -3655,7 +3667,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>58</v>
@@ -3720,7 +3732,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -3767,7 +3779,7 @@
         <v>36</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>34</v>
@@ -3794,7 +3806,7 @@
         <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>34</v>
@@ -3821,7 +3833,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>34</v>
@@ -3848,7 +3860,7 @@
         <v>36</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>58</v>
@@ -3967,7 +3979,7 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>53</v>
@@ -4014,7 +4026,7 @@
         <v>36</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>34</v>
@@ -4041,7 +4053,7 @@
         <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>34</v>
@@ -4068,7 +4080,7 @@
         <v>36</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
@@ -4095,7 +4107,7 @@
         <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>34</v>
@@ -4122,7 +4134,7 @@
         <v>36</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -4149,13 +4161,13 @@
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>50</v>
@@ -4187,7 +4199,7 @@
         <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>34</v>
@@ -4214,7 +4226,7 @@
         <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>34</v>
@@ -4241,7 +4253,7 @@
         <v>36</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>34</v>
@@ -4268,7 +4280,7 @@
         <v>36</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>58</v>
@@ -4295,7 +4307,7 @@
         <v>36</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>34</v>
@@ -4322,7 +4334,7 @@
         <v>36</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>58</v>
@@ -4349,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>34</v>
@@ -4376,13 +4388,13 @@
         <v>36</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>51</v>
@@ -4414,7 +4426,7 @@
         <v>36</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>34</v>
@@ -4441,7 +4453,7 @@
         <v>36</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>58</v>

--- a/work_node_memo.xlsx
+++ b/work_node_memo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\プログラミング\github\fact_sim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suzuk\OneDrive\デスクトップ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF73B18F-5663-4FBF-A705-9352786C81E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4950235-DD23-4D2E-8932-93C99EAE721F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="119">
   <si>
     <t>説明</t>
   </si>
@@ -133,13 +133,6 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>備考</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -1609,13 +1602,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>278059</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>165652</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>147312</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>38454</xdr:rowOff>
@@ -3359,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0103435C-BE91-42D6-9B0B-E3F858993823}">
-  <dimension ref="B1:I57"/>
+  <dimension ref="B1:H57"/>
   <sheetFormatPr defaultColWidth="113.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
@@ -3370,20 +3363,19 @@
     <col min="6" max="6" width="38.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3400,43 +3392,37 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="G5" s="2" t="str">
         <f>B6</f>
         <v>wait</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
@@ -3444,53 +3430,47 @@
         <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="str">
         <f t="shared" ref="G6:G7" si="0">B7</f>
         <v>down</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>idle</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
@@ -3498,31 +3478,28 @@
         <v>15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="8" t="str">
         <f>B5</f>
         <v>process</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -3539,54 +3516,48 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="2" t="str">
         <f>B15</f>
         <v>workIn2_idle</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B15" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>2</v>
@@ -3596,105 +3567,93 @@
         <v>process2</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>wait</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="str">
         <f t="shared" si="1"/>
         <v>down</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="6" t="str">
         <f t="shared" si="1"/>
         <v>workIn1_idle</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>2</v>
@@ -3704,18 +3663,15 @@
         <v>process1</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3732,27 +3688,24 @@
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>2</v>
@@ -3762,207 +3715,183 @@
         <v>workIn_idle</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" s="8" t="str">
         <f t="shared" ref="G26:G31" si="2">B27</f>
         <v>workIn_process</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27" s="2" t="str">
         <f t="shared" si="2"/>
         <v>workOut_wait</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G28" s="4" t="str">
         <f t="shared" si="2"/>
         <v>workOut_down</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B29" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G29" s="6" t="str">
         <f t="shared" si="2"/>
         <v>agvOut_wait</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G30" s="4" t="str">
         <f t="shared" si="2"/>
         <v>agvOut_down</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G31" s="6" t="str">
         <f t="shared" si="2"/>
         <v>agvIn_idle</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B32" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G32" s="8" t="str">
         <f>B25</f>
         <v>agv_process</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
@@ -3979,27 +3908,24 @@
         <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>2</v>
@@ -4009,176 +3935,155 @@
         <v>workIn_idle_1</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B37" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G37" s="8" t="str">
         <f t="shared" ref="G37:G41" si="3">B38</f>
         <v>workIn_process_1</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G38" s="2" t="str">
         <f t="shared" si="3"/>
         <v>workIn_idle_2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G39" s="8" t="str">
         <f t="shared" si="3"/>
         <v>workIn_process_2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G40" s="2" t="str">
         <f t="shared" si="3"/>
         <v>workIn_idle_3</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B41" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G41" s="8" t="str">
         <f t="shared" si="3"/>
         <v>workIn_process_3</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="1"/>
@@ -4186,226 +4091,201 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B44" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G44" s="8" t="str">
         <f>B45</f>
         <v>workIn_process_n</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G45" s="2" t="str">
         <f t="shared" ref="G45:G50" si="4">B46</f>
         <v>workOut_wait_1</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B46" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G46" s="4" t="str">
         <f t="shared" si="4"/>
         <v>workOut_down_1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B47" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G47" s="6" t="str">
         <f t="shared" si="4"/>
         <v>workOut_wait_2</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G48" s="4" t="str">
         <f t="shared" si="4"/>
         <v>workOut_down_2</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B49" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G49" s="6" t="str">
         <f t="shared" si="4"/>
         <v>workOut_wait_3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G50" s="4" t="str">
         <f t="shared" si="4"/>
         <v>workOut_down_3</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B51" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="1"/>
@@ -4413,141 +4293,125 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B53" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G53" s="4" t="str">
         <f>B54</f>
         <v>workOut_down_n</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B54" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G54" s="6" t="str">
         <f t="shared" ref="G54:G56" si="5">B55</f>
         <v>agvOut_wait</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G55" s="4" t="str">
         <f t="shared" si="5"/>
         <v>agvOut_down</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B56" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="F56" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="6" t="str">
         <f t="shared" si="5"/>
         <v>agvIn_idle</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B57" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G57" s="8" t="str">
         <f>B36</f>
         <v>agv_process</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
